--- a/Docs/Журнал_калибровки.xlsx
+++ b/Docs/Журнал_калибровки.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Журнал" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Замеры" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Журнал" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Замеры" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$-419]General"/>
+  </numFmts>
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,16 +27,41 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,15 +69,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Excel Built-in Normal" xfId="1"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -414,1012 +469,2904 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X10"/>
+  <dimension ref="A1:X38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9.140625" customWidth="1" style="6" min="1" max="1"/>
+    <col width="61.7109375" customWidth="1" style="6" min="2" max="2"/>
+    <col width="9.140625" customWidth="1" style="6" min="3" max="4"/>
+    <col width="5" customWidth="1" style="6" min="5" max="5"/>
+    <col width="4.28515625" customWidth="1" style="6" min="6" max="6"/>
+    <col width="5.140625" customWidth="1" style="6" min="7" max="7"/>
+    <col width="4.5703125" customWidth="1" style="6" min="8" max="8"/>
+    <col width="2.28515625" customWidth="1" style="6" min="9" max="9"/>
+    <col width="5.42578125" customWidth="1" style="6" min="10" max="10"/>
+    <col width="5.140625" customWidth="1" style="6" min="11" max="11"/>
+    <col width="9.140625" customWidth="1" style="6" min="12" max="12"/>
+    <col width="5.140625" customWidth="1" style="6" min="13" max="13"/>
+    <col width="9.140625" customWidth="1" style="6" min="14" max="22"/>
+    <col width="7" customWidth="1" style="6" min="23" max="23"/>
+    <col width="5.85546875" customWidth="1" style="6" min="24" max="24"/>
+    <col width="9.140625" customWidth="1" style="6" min="25" max="16384"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Обозначение</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Станок</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Материал</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Габарит 1, мм</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Габарит 2, мм</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Габарит 3, мм</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Квалитет</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Балл сложности</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Технология</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>Резка заготовки, ч</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>Резка заготовки, счёт</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>Программирование, ч</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>Программирование, счёт</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>Наладка, ч</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>Наладка, счёт</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>Обработка на станке, ч</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>Обработка на станке, счёт</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="3" t="inlineStr">
         <is>
           <t>Слесарная, ч</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="3" t="inlineStr">
         <is>
           <t>Слесарная, счёт</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="3" t="inlineStr">
         <is>
           <t>Финишная, ч</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="3" t="inlineStr">
         <is>
           <t>Финишная, счёт</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="3" t="inlineStr">
         <is>
           <t>Внутренний контроль, ч</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="3" t="inlineStr">
         <is>
           <t>Внутренний контроль, счёт</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>DEMO-01</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Пластина</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>VF2</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Д16Т</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>milling</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>штука</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
+      <c r="K2" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>разово</t>
         </is>
       </c>
-      <c r="O2" t="n">
+      <c r="O2" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>партия</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>штука</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>штука</t>
-        </is>
-      </c>
-      <c r="U2" t="n">
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="n">
         <v>0.05</v>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>штука</t>
-        </is>
-      </c>
-      <c r="W2" t="n">
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="W2" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X2" s="3" t="inlineStr">
         <is>
           <t>партия</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>DEMO-02</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Кронштейн</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>VF2</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Д16Т</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>milling</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="3" t="n">
         <v>0.15</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>штука</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>разово</t>
         </is>
       </c>
-      <c r="O3" t="n">
+      <c r="O3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>партия</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>штука</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>штука</t>
-        </is>
-      </c>
-      <c r="U3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>штука</t>
-        </is>
-      </c>
-      <c r="W3" t="n">
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X3" s="3" t="inlineStr">
         <is>
           <t>партия</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>DEMO-03</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Корпус</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>VF2</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Д16Т</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="3" t="n">
         <v>200</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>milling</t>
         </is>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>штука</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>разово</t>
         </is>
       </c>
-      <c r="O4" t="n">
+      <c r="O4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>партия</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q4" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>штука</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>штука</t>
-        </is>
-      </c>
-      <c r="U4" t="n">
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>штука</t>
-        </is>
-      </c>
-      <c r="W4" t="n">
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X4" s="3" t="inlineStr">
         <is>
           <t>партия</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>DEMO-04</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Крышка</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>SMM</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>АМг6</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>milling</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>штука</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
+      <c r="K5" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>разово</t>
         </is>
       </c>
-      <c r="O5" t="n">
+      <c r="O5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>партия</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q5" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>штука</t>
-        </is>
-      </c>
-      <c r="S5" t="n">
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>штука</t>
-        </is>
-      </c>
-      <c r="U5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>штука</t>
-        </is>
-      </c>
-      <c r="W5" t="n">
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X5" s="3" t="inlineStr">
         <is>
           <t>партия</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>DEMO-05</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Фланец</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>MV6</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Сталь 45</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>milling</t>
         </is>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>штука</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>разово</t>
         </is>
       </c>
-      <c r="O6" t="n">
+      <c r="O6" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P6" s="3" t="inlineStr">
         <is>
           <t>партия</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q6" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>штука</t>
-        </is>
-      </c>
-      <c r="S6" t="n">
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>штука</t>
-        </is>
-      </c>
-      <c r="U6" t="n">
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="n">
         <v>0.15</v>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>штука</t>
-        </is>
-      </c>
-      <c r="W6" t="n">
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X6" s="3" t="inlineStr">
         <is>
           <t>партия</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>DEMO-06</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Плита основания</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>VOLZH1</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Сталь 45</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="3" t="n">
         <v>400</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="3" t="n">
         <v>250</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>milling</t>
         </is>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>штука</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>разово</t>
         </is>
       </c>
-      <c r="O7" t="n">
+      <c r="O7" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P7" s="3" t="inlineStr">
         <is>
           <t>партия</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q7" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>штука</t>
-        </is>
-      </c>
-      <c r="S7" t="n">
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>штука</t>
-        </is>
-      </c>
-      <c r="U7" t="n">
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>штука</t>
-        </is>
-      </c>
-      <c r="W7" t="n">
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X7" s="3" t="inlineStr">
         <is>
           <t>партия</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>DEMO-07</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Вал</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>ST20Y</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>40Х</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="3" t="n">
         <v>180</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>turning</t>
         </is>
       </c>
-      <c r="K8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>штука</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
+      <c r="K8" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>разово</t>
         </is>
       </c>
-      <c r="O8" t="n">
+      <c r="O8" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P8" s="3" t="inlineStr">
         <is>
           <t>партия</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="Q8" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>штука</t>
-        </is>
-      </c>
-      <c r="S8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>штука</t>
-        </is>
-      </c>
-      <c r="U8" t="n">
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="n">
         <v>0.05</v>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>штука</t>
-        </is>
-      </c>
-      <c r="W8" t="n">
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X8" s="3" t="inlineStr">
         <is>
           <t>партия</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>DEMO-08</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Втулка</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>ST20Y</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>12Х18Н10Т</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>turning</t>
         </is>
       </c>
-      <c r="K9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>штука</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
+      <c r="K9" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N9" s="3" t="inlineStr">
         <is>
           <t>разово</t>
         </is>
       </c>
-      <c r="O9" t="n">
+      <c r="O9" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P9" s="3" t="inlineStr">
         <is>
           <t>партия</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q9" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>штука</t>
-        </is>
-      </c>
-      <c r="S9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>штука</t>
-        </is>
-      </c>
-      <c r="U9" t="n">
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T9" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="U9" s="3" t="n">
         <v>0.05</v>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>штука</t>
-        </is>
-      </c>
-      <c r="W9" t="n">
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X9" s="3" t="inlineStr">
         <is>
           <t>партия</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>DEMO-09</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Корпус точный</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>SMM</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>12Х18Н10Т</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>milling</t>
         </is>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>штука</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N10" s="3" t="inlineStr">
         <is>
           <t>разово</t>
         </is>
       </c>
-      <c r="O10" t="n">
+      <c r="O10" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P10" s="3" t="inlineStr">
         <is>
           <t>партия</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q10" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>штука</t>
-        </is>
-      </c>
-      <c r="S10" t="n">
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>штука</t>
-        </is>
-      </c>
-      <c r="U10" t="n">
+      <c r="T10" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>штука</t>
-        </is>
-      </c>
-      <c r="W10" t="n">
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X10" s="3" t="inlineStr">
         <is>
           <t>партия</t>
         </is>
       </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>XWS.65.A.P001050</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>XWS.65.A.P001050 Кронштейн [A.1]</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>VF2</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>AW 6061 T6</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>milling</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N11" s="3" t="n"/>
+      <c r="O11" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P11" s="3" t="n"/>
+      <c r="Q11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" s="3" t="n"/>
+      <c r="S11" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T11" s="3" t="n"/>
+      <c r="U11" s="3" t="n"/>
+      <c r="V11" s="3" t="n"/>
+      <c r="W11" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>МБЦР.141.040.033-02</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>МБЦР.141.040.033-02 Рамка задняя [A.1]</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>VF2</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Д16Т</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>137.6</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>121.6</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>milling</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N12" s="3" t="n"/>
+      <c r="O12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" s="3" t="n"/>
+      <c r="Q12" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R12" s="3" t="n"/>
+      <c r="S12" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T12" s="3" t="n"/>
+      <c r="U12" s="3" t="n"/>
+      <c r="V12" s="3" t="n"/>
+      <c r="W12" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>МБЦР.107.000.320-02</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>МБЦР.107.000.320-02 Радиатор [A.1]</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>VF2</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>AW 6061</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>125.8</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>milling</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N13" s="3" t="n"/>
+      <c r="O13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P13" s="3" t="n"/>
+      <c r="Q13" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R13" s="3" t="n"/>
+      <c r="S13" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T13" s="3" t="n"/>
+      <c r="U13" s="3" t="n"/>
+      <c r="V13" s="3" t="n"/>
+      <c r="W13" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>XWS.65.A.1.P000630</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>XWS.65.A.1.P000630 Пластина</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>VF2</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>AW 6061 T6</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>milling</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N14" s="3" t="n"/>
+      <c r="O14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" s="3" t="n"/>
+      <c r="Q14" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R14" s="3" t="n"/>
+      <c r="S14" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T14" s="3" t="n"/>
+      <c r="U14" s="3" t="n"/>
+      <c r="V14" s="3" t="n"/>
+      <c r="W14" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>XWS.65.A.1.P000629</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>XWS.65.A.1.P000629 Фланец</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>VF2</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>AW 6061 T6</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>milling</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N15" s="3" t="n"/>
+      <c r="O15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" s="3" t="n"/>
+      <c r="Q15" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R15" s="3" t="n"/>
+      <c r="S15" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T15" s="3" t="n"/>
+      <c r="U15" s="3" t="n"/>
+      <c r="V15" s="3" t="n"/>
+      <c r="W15" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>XWS.A.P000164</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>XWS.A.P000164 Крышка лазера IPG [A.1]</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>VF2</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>POM-C</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>milling</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N16" s="3" t="n"/>
+      <c r="O16" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P16" s="3" t="n"/>
+      <c r="Q16" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="R16" s="3" t="n"/>
+      <c r="S16" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T16" s="3" t="n"/>
+      <c r="U16" s="3" t="n"/>
+      <c r="V16" s="3" t="n"/>
+      <c r="W16" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X16" s="3" t="n"/>
+    </row>
+    <row r="17" customFormat="1" s="9">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>MBIS.AI.P3.48000.01</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>MBIS.AI.P3.48000.01 Основание [A.1]</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>VF2</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>12Х18Н10Т</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="I17" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t>milling</t>
+        </is>
+      </c>
+      <c r="K17" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L17" s="8" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="M17" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N17" s="8" t="n"/>
+      <c r="O17" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" s="8" t="n"/>
+      <c r="Q17" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R17" s="8" t="n"/>
+      <c r="S17" s="11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T17" s="8" t="n"/>
+      <c r="U17" s="8" t="n"/>
+      <c r="V17" s="8" t="n"/>
+      <c r="W17" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X17" s="8" t="n"/>
+    </row>
+    <row r="18" customFormat="1" s="9">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>MBIS.AI1.M1.316000.01</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>MBIS.AI1.M1.316000.01 Стойка</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>ST20Y</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Д16Т</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="G18" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="I18" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>turning</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L18" s="8" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="M18" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N18" s="10" t="n"/>
+      <c r="O18" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="P18" s="10" t="n"/>
+      <c r="Q18" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="R18" s="10" t="n"/>
+      <c r="S18" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T18" s="10" t="n"/>
+      <c r="U18" s="10" t="n"/>
+      <c r="V18" s="10" t="n"/>
+      <c r="W18" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X18" s="10" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>МБЦР.107.000.181</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>МБЦР.107.000.181 Фланец передний [A.1]</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>AW 6061</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>milling</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N19" s="3" t="n"/>
+      <c r="O19" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P19" s="3" t="n"/>
+      <c r="Q19" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R19" s="3" t="n"/>
+      <c r="S19" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T19" s="3" t="n"/>
+      <c r="U19" s="3" t="n"/>
+      <c r="V19" s="3" t="n"/>
+      <c r="W19" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>XWS.PSU.A.1.P000309</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>XWS.PSU.A.1.P000309 Радиатор платы термоконтроллера [A.1]</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Д16Т</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>milling</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N20" s="3" t="n"/>
+      <c r="O20" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P20" s="3" t="n"/>
+      <c r="Q20" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="R20" s="3" t="n"/>
+      <c r="S20" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T20" s="3" t="n"/>
+      <c r="U20" s="3" t="n"/>
+      <c r="V20" s="3" t="n"/>
+      <c r="W20" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>МБЦР.140.100.021-01</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>МБЦР.140.100.021-01 Крышка [A.1]</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>AW 6061</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>milling</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" s="3" t="n"/>
+      <c r="O21" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P21" s="3" t="n"/>
+      <c r="Q21" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="R21" s="3" t="n"/>
+      <c r="S21" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T21" s="3" t="n"/>
+      <c r="U21" s="3" t="n"/>
+      <c r="V21" s="3" t="n"/>
+      <c r="W21" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>МБЦР.107.000.070-01</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>МБЦР.107.000.070-01 Заглушка верхняя</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Сплав 6061</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>milling</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N22" s="3" t="n"/>
+      <c r="O22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" s="3" t="n"/>
+      <c r="Q22" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="R22" s="3" t="n"/>
+      <c r="S22" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T22" s="3" t="n"/>
+      <c r="U22" s="3" t="n"/>
+      <c r="V22" s="3" t="n"/>
+      <c r="W22" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X22" s="3" t="n"/>
+    </row>
+    <row r="23" customFormat="1" s="7">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>XWS.PSU.A.1.P000310</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>XWS.PSU.A.1.P000310 Радиатор платы драйвера лазера [A.1]</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>SMM</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Д16Т</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>milling</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N23" s="3" t="n"/>
+      <c r="O23" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P23" s="3" t="n"/>
+      <c r="Q23" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="R23" s="3" t="n"/>
+      <c r="S23" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T23" s="3" t="n"/>
+      <c r="U23" s="3" t="n"/>
+      <c r="V23" s="3" t="n"/>
+      <c r="W23" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X23" s="3" t="n"/>
+    </row>
+    <row r="24" s="6">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>MBIS.Al1.M1.310000.11</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>MBIS.Al1.M1.310000.11</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>ST20Y</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>turning</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N24" s="2" t="n"/>
+      <c r="O24" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P24" s="2" t="n"/>
+      <c r="Q24" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R24" s="2" t="n"/>
+      <c r="S24" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T24" s="2" t="n"/>
+      <c r="U24" s="2" t="n"/>
+      <c r="V24" s="2" t="n"/>
+      <c r="W24" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>MBIS.AI1.M1.316100.02</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>MBIS.AI1.M1.316100.02 Полумуфта</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>ST20Y</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>12Х18Н9Т</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>turning</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N25" s="2" t="n"/>
+      <c r="O25" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P25" s="2" t="n"/>
+      <c r="Q25" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R25" s="2" t="n"/>
+      <c r="S25" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T25" s="2" t="n"/>
+      <c r="U25" s="2" t="n"/>
+      <c r="V25" s="2" t="n"/>
+      <c r="W25" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>MBIS.AI.P4.190000.04-01</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>MBIS.AI.P4.190000.04-01 Ловитель [A.1]</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>ST20Y</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Д16Т</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>turning</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N26" s="2" t="n"/>
+      <c r="O26" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="P26" s="2" t="n"/>
+      <c r="Q26" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R26" s="2" t="n"/>
+      <c r="S26" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T26" s="2" t="n"/>
+      <c r="U26" s="2" t="n"/>
+      <c r="V26" s="2" t="n"/>
+      <c r="W26" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>MBIS.AI.P4.11110.15</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>MBIS.AI.P4.11110.15 Шпилька заземления приварная [A.1]</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>ST20Y</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>AISI 316</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>turning</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" s="2" t="n"/>
+      <c r="O27" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P27" s="2" t="n"/>
+      <c r="Q27" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="R27" s="2" t="n"/>
+      <c r="S27" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T27" s="2" t="n"/>
+      <c r="U27" s="2" t="n"/>
+      <c r="V27" s="2" t="n"/>
+      <c r="W27" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>MBIS.AI.P3.48000.02</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>MBIS.AI.P3.48000.02 Вал [B.1]</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>ST20Y</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>ЛС 59-1</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>148.5</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>turning</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N28" s="2" t="n"/>
+      <c r="O28" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P28" s="2" t="n"/>
+      <c r="Q28" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R28" s="2" t="n"/>
+      <c r="S28" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T28" s="2" t="n"/>
+      <c r="U28" s="2" t="n"/>
+      <c r="V28" s="2" t="n"/>
+      <c r="W28" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X28" s="2" t="n"/>
+    </row>
+    <row r="29" customFormat="1" s="9">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>MBIS.AI.P3.48000.01</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>MBIS.AI.P3.48000.01 Основание [A.1]</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>ST20Y</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>12Х18Н10Т</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="F29" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="G29" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="H29" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="I29" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J29" s="8" t="inlineStr">
+        <is>
+          <t>turning</t>
+        </is>
+      </c>
+      <c r="K29" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="M29" s="10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N29" s="10" t="n"/>
+      <c r="O29" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="P29" s="10" t="n"/>
+      <c r="Q29" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R29" s="10" t="n"/>
+      <c r="S29" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T29" s="10" t="n"/>
+      <c r="U29" s="10" t="n"/>
+      <c r="V29" s="10" t="n"/>
+      <c r="W29" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X29" s="10" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>MBIS.AI1.M2.410000.01</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>MBIS.AI1.M2.410000.01 Ось</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>ST20Y</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>АМг6</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>turning</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="N30" s="2" t="n"/>
+      <c r="O30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P30" s="2" t="n"/>
+      <c r="Q30" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="R30" s="2" t="n"/>
+      <c r="S30" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T30" s="2" t="n"/>
+      <c r="U30" s="2" t="n"/>
+      <c r="V30" s="2" t="n"/>
+      <c r="W30" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X30" s="2" t="n"/>
+    </row>
+    <row r="31" customFormat="1" s="9">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>MBIS.AI1.M1.316000.01</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>MBIS.AI1.M1.316000.01 Стойка</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>ST20Y</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>Д16Т</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="G31" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="H31" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="I31" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J31" s="8" t="inlineStr">
+        <is>
+          <t>turning</t>
+        </is>
+      </c>
+      <c r="K31" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L31" s="8" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="M31" s="10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N31" s="10" t="n"/>
+      <c r="O31" s="10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P31" s="10" t="n"/>
+      <c r="Q31" s="10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R31" s="10" t="n"/>
+      <c r="S31" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T31" s="10" t="n"/>
+      <c r="U31" s="10" t="n"/>
+      <c r="V31" s="10" t="n"/>
+      <c r="W31" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X31" s="10" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>MBIS.AI.P3.45100.04</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>MBIS.AI.P3.45100.04 Ось [A.1]</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>ST20Y</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>12Х18Н10Т</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>turning</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" s="2" t="n"/>
+      <c r="O32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P32" s="2" t="n"/>
+      <c r="Q32" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R32" s="2" t="n"/>
+      <c r="S32" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T32" s="2" t="n"/>
+      <c r="U32" s="2" t="n"/>
+      <c r="V32" s="2" t="n"/>
+      <c r="W32" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>MBIS.AI.18000.02</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>MBIS.AI.18000.02 Болт</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>ST20Y</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>AISI 316</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>turning</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N33" s="2" t="n"/>
+      <c r="O33" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P33" s="2" t="n"/>
+      <c r="Q33" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="R33" s="2" t="n"/>
+      <c r="S33" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T33" s="2" t="n"/>
+      <c r="U33" s="2" t="n"/>
+      <c r="V33" s="2" t="n"/>
+      <c r="W33" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>MBIS.AI.11000.16</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>MBIS.AI.11000.16 Втулка [A.1]</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>ST20Y</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>AISI 316</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>turning</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" s="2" t="n"/>
+      <c r="O34" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P34" s="2" t="n"/>
+      <c r="Q34" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R34" s="2" t="n"/>
+      <c r="S34" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T34" s="2" t="n"/>
+      <c r="U34" s="2" t="n"/>
+      <c r="V34" s="2" t="n"/>
+      <c r="W34" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X34" s="2" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>MBIS.AI1.M2.360000.05</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>MBIS.AI1.M2.360000.05 Кольцо [B.1]</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>ST20Y</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Д16Т</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>turning</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N35" s="2" t="n"/>
+      <c r="O35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P35" s="2" t="n"/>
+      <c r="Q35" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="R35" s="2" t="n"/>
+      <c r="S35" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T35" s="2" t="n"/>
+      <c r="U35" s="2" t="n"/>
+      <c r="V35" s="2" t="n"/>
+      <c r="W35" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>MBIS.AI.P4.10000.04</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>MBIS.AI.P4.10000.04 Стойка электрощита [A.1]</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>ST20Y</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>ЛС 59-1</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>turning</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>штука</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N36" s="2" t="n"/>
+      <c r="O36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P36" s="2" t="n"/>
+      <c r="Q36" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R36" s="2" t="n"/>
+      <c r="S36" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T36" s="2" t="n"/>
+      <c r="U36" s="2" t="n"/>
+      <c r="V36" s="2" t="n"/>
+      <c r="W36" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X36" s="2" t="n"/>
+    </row>
+    <row r="37">
+      <c r="C37" s="5" t="n"/>
+      <c r="J37" s="5" t="n"/>
+      <c r="K37" s="5" t="n"/>
+      <c r="L37" s="5" t="n"/>
+      <c r="W37" s="5" t="n"/>
+    </row>
+    <row r="38">
+      <c r="C38" s="5" t="n"/>
+      <c r="J38" s="5" t="n"/>
+      <c r="K38" s="5" t="n"/>
+      <c r="L38" s="5" t="n"/>
+      <c r="W38" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Docs/Журнал_калибровки.xlsx
+++ b/Docs/Журнал_калибровки.xlsx
@@ -1735,7 +1735,7 @@
         <v>25.5</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>23</v>
+        <v>22.5</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>9</v>
@@ -2023,10 +2023,10 @@
         <v>50</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H18" s="10" t="n">
         <v>7</v>
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>148.5</v>
+        <v>144</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>14.5</v>
@@ -2947,10 +2947,10 @@
         <v>50</v>
       </c>
       <c r="F31" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H31" s="10" t="n">
         <v>7</v>
